--- a/artfynd/A 30067-2025 artfynd.xlsx
+++ b/artfynd/A 30067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126203936</v>
       </c>
       <c r="B2" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>126203951</v>
       </c>
       <c r="B3" t="n">
-        <v>58507</v>
+        <v>58511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30067-2025 artfynd.xlsx
+++ b/artfynd/A 30067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126203936</v>
       </c>
       <c r="B2" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>126203951</v>
       </c>
       <c r="B3" t="n">
-        <v>58511</v>
+        <v>58514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30067-2025 artfynd.xlsx
+++ b/artfynd/A 30067-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>133456627</v>
       </c>
       <c r="B4" t="n">
-        <v>58831</v>
+        <v>58838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30067-2025 artfynd.xlsx
+++ b/artfynd/A 30067-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>133456627</v>
       </c>
       <c r="B4" t="n">
-        <v>58838</v>
+        <v>58848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
